--- a/kits/replication-package/samples/2-check-report/check_report.xlsx
+++ b/kits/replication-package/samples/2-check-report/check_report.xlsx
@@ -479,7 +479,7 @@
     <t xml:space="preserve">F34</t>
   </si>
   <si>
-    <t xml:space="preserve">.DS_Store</t>
+    <t xml:space="preserve">output/Thumbs.db</t>
   </si>
   <si>
     <t xml:space="preserve">1 stray system or temporary file(s) or folder(s).</t>
